--- a/sample/jira-ru.xlsx
+++ b/sample/jira-ru.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,7 +448,7 @@
         <v>2026-08-24 09:12</v>
       </c>
       <c r="F2" t="str">
-        <v>2026.08.26 18:02</v>
+        <v>26.08.2026 18:02</v>
       </c>
       <c r="G2" t="str">
         <v>Готово</v>
@@ -640,7 +640,7 @@
         <v>2026-08-28 09:00</v>
       </c>
       <c r="F8" t="str">
-        <v>2026.08.29 15:30</v>
+        <v>29.08.2026 15:30</v>
       </c>
       <c r="G8" t="str">
         <v>Готово</v>
@@ -687,9 +687,41 @@
         <v>2026-08-28 11:00</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>INC-109</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Пример из письма</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-08-13 11:20</v>
+      </c>
+      <c r="F10" t="str">
+        <v>11.08.2026 13:37</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Готово</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Марат</v>
+      </c>
+      <c r="J10" t="str">
+        <v>2026-08-13 13:40</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
   </ignoredErrors>
 </worksheet>
 </file>